--- a/admin/public/imports/item/th.xlsx
+++ b/admin/public/imports/item/th.xlsx
@@ -1,56 +1,231 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10916"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macos-1/Desktop/物品批量导入模版/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E351912-EF1F-BE4F-851C-D317F1C7A7C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30100" yWindow="8240" windowWidth="35720" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="15000"/>
   </bookViews>
   <sheets>
     <sheet name="物品导入模板" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
-    <t>1.00</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ชื่อสินค้า</t>
+    </r>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="222"/>
+      </rPr>
+      <t>ประเภทสินค้า</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="222"/>
+      </rPr>
+      <t>สามารถกรอกได้เฉพาะชื่อประเภทที่มีอยู่ในระบบ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
-    <t>819238310231</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">บาร์โค้ดสินค้า
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">(ขั้นต่ำ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> หลัก สูงสุด</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> 13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> หลัก รองรับเฉพาะตัวเลข)</t>
+    </r>
   </si>
   <si>
-    <t>100.000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>เปิดใช้งานหรือไม่</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>เปิดใช้งาน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Tahoma"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ปิดใช้งาน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=0)</t>
+    </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -58,15 +233,56 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="4"/>
         <charset val="222"/>
       </rPr>
-      <t>ชื่อสินค้า</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+      <t>หน่วยพื้นฐาน</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="222"/>
+      </rPr>
+      <t>สามารถกรอกได้เฉพาะชื่อหน่วยที่มีอยู่ในระบบ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+      </rPr>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>*</t>
     </r>
     <r>
@@ -74,17 +290,36 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="4"/>
         <charset val="222"/>
       </rPr>
-      <t>ประเภทสินค้า</t>
-    </r>
+      <t>อัตราการประเมินค่า</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
-        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Angsana New"/>
+        <charset val="222"/>
+      </rPr>
+      <t>สต็อกเริ่มต้น</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -93,8 +328,8 @@
       <rPr>
         <sz val="9"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>(</t>
     </r>
@@ -103,320 +338,57 @@
         <sz val="9"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="4"/>
         <charset val="222"/>
       </rPr>
-      <t>สามารถกรอกได้เฉพาะชื่อประเภทที่มีอยู่ในระบบ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
+      <t>สต็อกเริ่มต้นของสินค้า</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <r>
-      <t>*</t>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="4"/>
         <charset val="222"/>
       </rPr>
-      <t>เปิดใช้งานหรือไม่</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>ตัวอย่าง</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="4"/>
         <charset val="222"/>
       </rPr>
-      <t>เปิดใช้งาน</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=0/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ปิดใช้งาน</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>=1)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>หน่วยพื้นฐาน</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>สามารถกรอกได้เฉพาะชื่อหน่วยที่มีอยู่ในระบบ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>อัตราการประเมินค่า</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>*</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>สต็อกเริ่มต้น</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>สต็อกเริ่มต้นของสินค้า</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>kg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">บาร์โค้ดสินค้า
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">(ขั้นต่ำ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> หลัก สูงสุด</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> หลัก รองรับเฉพาะตัวเลข)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
-      <t>ตัวอย่าง</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="4"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Angsana New"/>
-        <family val="4"/>
-        <charset val="222"/>
-      </rPr>
       <t>กรุณาลบแถวนี้เมื่อทำการนำเข้า</t>
     </r>
     <r>
@@ -424,7 +396,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -437,7 +408,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="1"/>
         <charset val="134"/>
       </rPr>
       <t>ภาษาไทย</t>
@@ -447,7 +417,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -458,7 +427,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Angsana New"/>
-        <family val="1"/>
         <charset val="134"/>
       </rPr>
       <t>พุดดิ้งคาราเมล</t>
@@ -468,7 +436,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -483,7 +450,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Myanmar Text"/>
-        <family val="4"/>
         <charset val="134"/>
       </rPr>
       <t>မြန်မာဘာသာ</t>
@@ -493,7 +459,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -504,7 +469,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Myanmar Text"/>
-        <family val="4"/>
         <charset val="134"/>
       </rPr>
       <t>ရွှင်ဆူမန်</t>
@@ -514,7 +478,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -527,7 +490,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Batang"/>
-        <family val="1"/>
         <charset val="129"/>
       </rPr>
       <t>한국어</t>
@@ -537,7 +499,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -548,7 +509,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Batang"/>
-        <family val="1"/>
         <charset val="129"/>
       </rPr>
       <t>크림</t>
@@ -558,7 +518,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -569,7 +528,6 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Batang"/>
-        <family val="1"/>
         <charset val="129"/>
       </rPr>
       <t>브륄레</t>
@@ -579,135 +537,299 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <family val="4"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
 Svenska:Karamellpudding</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>819238310231</t>
   </si>
   <si>
     <t>1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>1.00</t>
+  </si>
+  <si>
+    <t>100.000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="37">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Angsana New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Angsana New"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Angsana New"/>
-      <family val="1"/>
+      <charset val="222"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Angsana New"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Myanmar Text"/>
-      <family val="4"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Batang"/>
-      <family val="1"/>
       <charset val="129"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Angsana New"/>
-      <family val="4"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Angsana New"/>
-      <family val="4"/>
-      <charset val="222"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -716,12 +838,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -744,9 +1052,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -754,47 +1304,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FFFF3300"/>
+      <color rgb="00FF3300"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1052,75 +1646,75 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83035714285714" defaultRowHeight="12.4" outlineLevelRow="1" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="22.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="25.8303571428571" customWidth="1"/>
+    <col min="3" max="3" width="22.6607142857143" customWidth="1"/>
+    <col min="4" max="4" width="20.8303571428571" customWidth="1"/>
     <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="15.1640625" customWidth="1"/>
-    <col min="7" max="7" width="30.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.1607142857143" customWidth="1"/>
+    <col min="7" max="7" width="30.1607142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="48">
-      <c r="A1" s="4" t="s">
+    <row r="1" s="1" customFormat="1" ht="51" spans="1:7">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" s="2" customFormat="1" ht="166" spans="1:7">
+      <c r="A2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="3" customFormat="1" ht="170">
-      <c r="A2" s="1" t="s">
+      <c r="F2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="G2" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="F2:G2 C2:D2" numberStoredAsText="1"/>
+    <ignoredError sqref="C2:D2 F2:G2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>